--- a/results/Int Task Remove ACC -0.3/Rando_6_permute.xlsx
+++ b/results/Int Task Remove ACC -0.3/Rando_6_permute.xlsx
@@ -440,337 +440,337 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6511754499370599</v>
+        <v>0.664959911089942</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6540545367944748</v>
+        <v>0.6501377879086858</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6568542396715771</v>
+        <v>0.6580591750870388</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6484055160525748</v>
+        <v>0.6547576520486738</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6462720715816691</v>
+        <v>0.6547675750462129</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6449891697569716</v>
+        <v>0.6533301579741209</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6563864412161626</v>
+        <v>0.6599984123203937</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6588430918926276</v>
+        <v>0.6657863550278411</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6541594370541739</v>
+        <v>0.6638570407920252</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6585454019664546</v>
+        <v>0.663827271799408</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6648947028203994</v>
+        <v>0.6664724594291158</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6692608217376019</v>
+        <v>0.6642100159902018</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6692608217376019</v>
+        <v>0.6664228444414202</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6692608217376019</v>
+        <v>0.66433901495821</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6808806518558841</v>
+        <v>0.6632800893636807</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6783743861917236</v>
+        <v>0.6632800893636807</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6796076730287257</v>
+        <v>0.6670394878599213</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6730584946529219</v>
+        <v>0.6676660542759614</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6523279352226721</v>
+        <v>0.666393075448803</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6523279352226721</v>
+        <v>0.6647713741366992</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6690496036471268</v>
+        <v>0.665681454768142</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6705664046995317</v>
+        <v>0.6660046609737011</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6536009140498305</v>
+        <v>0.6514603817235396</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6548738928769888</v>
+        <v>0.6501874028963812</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6444689211717076</v>
+        <v>0.649854273693283</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6484721418931945</v>
+        <v>0.6485812948661246</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6129931729776931</v>
+        <v>0.6520472561494233</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.623977931253473</v>
+        <v>0.6525547465949944</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6295971830027558</v>
+        <v>0.6639619410517243</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6189909162045385</v>
+        <v>0.6700092992662652</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6215666428514726</v>
+        <v>0.6690255049388176</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6212434366459134</v>
+        <v>0.6706117669739962</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6199761281030631</v>
+        <v>0.676976661109788</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6358330781705395</v>
+        <v>0.6602847616779506</v>
       </c>
     </row>
     <row r="36">
@@ -780,27 +780,27 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6358330781705395</v>
+        <v>0.6602847616779506</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6355197949625194</v>
+        <v>0.6622140759137664</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6588601027455516</v>
+        <v>0.6649088785311695</v>
       </c>
     </row>
     <row r="39">
@@ -810,517 +810,517 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6538178024246135</v>
+        <v>0.6722632372787172</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.656110014856145</v>
+        <v>0.6437913221968949</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6543252928701845</v>
+        <v>0.6424389593894237</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6607596479887502</v>
+        <v>0.6411461345671872</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6901926762607877</v>
+        <v>0.6408923893444017</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6905059594688078</v>
+        <v>0.6542572494584878</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6905059594688078</v>
+        <v>0.6536108370473696</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6900835232878577</v>
+        <v>0.6584702706993728</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6929626101452726</v>
+        <v>0.6584702706993728</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6411815738441126</v>
+        <v>0.6568046246838817</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6405252384354552</v>
+        <v>0.6567606799804941</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6178625296272355</v>
+        <v>0.6584660179861418</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6293788770568957</v>
+        <v>0.6412666281087334</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6293788770568957</v>
+        <v>0.6542643373138729</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6333466585014573</v>
+        <v>0.6586049399516892</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6151946608602955</v>
+        <v>0.6775692058199798</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6104316220415291</v>
+        <v>0.6606632531555132</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5553079531407705</v>
+        <v>0.6476697966636047</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5512352714365099</v>
+        <v>0.6423439821272638</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.529068712505245</v>
+        <v>0.6457362297145579</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5182597330430148</v>
+        <v>0.6443682736252396</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5082771975186836</v>
+        <v>0.6429648782589958</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4938789280894544</v>
+        <v>0.6130116014016942</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4884638065752617</v>
+        <v>0.6355594869526757</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4844152235793103</v>
+        <v>0.6358642647342339</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4858072783769378</v>
+        <v>0.5625276426360017</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4882384127740165</v>
+        <v>0.5588660565440752</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4795515372140759</v>
+        <v>0.5753793420202089</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4795515372140759</v>
+        <v>0.5341195182526451</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4860681114551084</v>
+        <v>0.533800564760317</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4815077853003549</v>
+        <v>0.533800564760317</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4891456582633054</v>
+        <v>0.5475070595039635</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5037253767903922</v>
+        <v>0.5830469839757766</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5059339525283798</v>
+        <v>0.5829675999954638</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5302438789280894</v>
+        <v>0.5710273988137765</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5311681352703025</v>
+        <v>0.5730460200274442</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5428985359325916</v>
+        <v>0.5864477369895327</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5472107871488676</v>
+        <v>0.5864477369895327</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5407565860352238</v>
+        <v>0.5746450402023158</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5405524558001338</v>
+        <v>0.5892460222955579</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5385040655938489</v>
+        <v>0.5772477006997131</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5462468388164983</v>
+        <v>0.5788736547250479</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.544367139568378</v>
+        <v>0.524655813742501</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5352379818324091</v>
+        <v>0.5261626917973667</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.522091427664183</v>
+        <v>0.4973193730933669</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5122421438210911</v>
+        <v>0.4923607094659726</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5277546241168531</v>
+        <v>0.4938179725331428</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5202018054185237</v>
+        <v>0.4839219088445095</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5147030472107872</v>
+        <v>0.4826886220075075</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5148575624581817</v>
+        <v>0.5005443472935733</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5138879438415043</v>
+        <v>0.5016840744394924</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5139318885448916</v>
+        <v>0.5019874346499733</v>
       </c>
     </row>
   </sheetData>
